--- a/DOSSIES_MULTIFORMATO/BANCO_MASTER/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/BANCO_MASTER/dossie.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -2638,9 +2638,2510 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Serviços</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Comp.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Atraso</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Corrigido</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>150448</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>05/2024</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>34.862,00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>653 dias</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>059/2024</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>150496</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>05/2024</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10.290,00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>652 dias</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>151276</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>06/2024</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>35.710,00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>623 dias</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>059/2024</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>151274</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>06/2024</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10.092,00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>623 dias</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>059/2024</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>152004</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>07/2024</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9.878,00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>590 dias</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>152037</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>07/2024</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>36.068,00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>590 dias</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>059/2024</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>152835</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>08/2024</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>9.744,00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>560 dias</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>152834</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>08/2024</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>36.818,00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>560 dias</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>059/2024</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>153593</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>09/2024</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9.470,00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>531 dias</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>153594</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>09/2024</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>36.750,00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>531 dias</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>059/2024</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>154379</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10/2024</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9.192,00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>497 dias</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>154386</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10/2024</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>35.928,00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>497 dias</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>059/2024</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>155237</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8.878,00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>469 dias</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>155238</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>36.216,00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>469 dias</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>155750</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>36.934,00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>444 dias</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>155979</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8.624,00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>444 dias</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>156592</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>01/2025</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8.434,00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>414 dias</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>156830</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>01/2025</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>37.186,00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>405 dias</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>157594</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8.236,00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>377 dias</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>157592</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>37.240,00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>377 dias</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>158325</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8.076,00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>350 dias</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>158299</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>37.270,00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>350 dias</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>159145</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>36.610,00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>317 dias</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>159144</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>7.634,00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>317 dias</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>159773</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>05/2025</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>7.370,00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>293 dias</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>159911</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>05/2025</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>37.240,00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>289 dias</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>002/2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>160040</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>587,02</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>275 dias</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>002/2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>160042</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>05/2025</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1.014,23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>275 dias</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>002/2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>160041</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>846,30</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>275 dias</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>002/2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>160759</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1.162,37</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>259 dias</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>160667</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>7.200,00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>259 dias</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>160770</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>37.516,00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>255 dias</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>161388</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>7.010,00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>232 dias</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>161396</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>37.482,00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>232 dias</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>002/2025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>161586</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1.308,15</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>224 dias</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>162382</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>37.054,00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>195 dias</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>162395</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>6.710,00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>195 dias</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>002/2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>162393</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1.397,46</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>195 dias</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>002/2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>163099</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>790,51</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>164 dias</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>163151</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>34.706,00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>163 dias</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>163150</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5.798,00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>163 dias</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>163830</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>5.314,00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>140 dias</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>002/2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>163961</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.697,54</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>134 dias</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>163960</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>32.838,00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>134 dias</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>164845</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4.904,00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>104 dias</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>164846</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>32.720,00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>104 dias</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>002/2025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>164847</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1.660,80</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>104 dias</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>122/2023</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>165490</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>32.530,00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>80 dias</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>165508</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4.594,00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>80 dias</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>002/2025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>165661</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1.680,49</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>72 dias</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BANCO MASTER S/A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>166400</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>01/2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>4.104,00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>42 dias</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>